--- a/data/00981A/20260814.xlsx
+++ b/data/00981A/20260814.xlsx
@@ -107,7 +107,7 @@
     <t xml:space="preserve">TX</t>
   </si>
   <si>
-    <t xml:space="preserve">台指期貨</t>
+    <t xml:space="preserve">台指期貨(B)</t>
   </si>
   <si>
     <t xml:space="preserve">679</t>
